--- a/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
+++ b/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\MTGPR_Tm_Hfus_Hf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E51EF8-CF38-49B5-B9F1-0629163767F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B8203-B464-4025-BF9F-E8A8C5D32FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{535DD4A0-2912-47A9-820B-218FC7178EC0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="57">
   <si>
     <t>tetrabutylammonium bromide</t>
   </si>
@@ -68,12 +68,6 @@
     <t>SMILES</t>
   </si>
   <si>
-    <t>tetraethylammonium bromide</t>
-  </si>
-  <si>
-    <t>CC[N+](CC)(CC)CC.[Br-]</t>
-  </si>
-  <si>
     <t>tetramethylammonium chloride</t>
   </si>
   <si>
@@ -192,6 +186,30 @@
   </si>
   <si>
     <t>[BH4-].[Na+]</t>
+  </si>
+  <si>
+    <t>butylamine borane</t>
+  </si>
+  <si>
+    <t>CCCCN.[B]</t>
+  </si>
+  <si>
+    <t>hexylamine borane</t>
+  </si>
+  <si>
+    <t>CCCCCCN.[B]</t>
+  </si>
+  <si>
+    <t>decylamine borane</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCN.[B]</t>
+  </si>
+  <si>
+    <t>octylamine borane</t>
+  </si>
+  <si>
+    <t>CCCCCCCCN.[B]</t>
   </si>
 </sst>
 </file>
@@ -563,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4AABDE-AFF5-4072-A990-39ABD46EABEB}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -621,10 +639,10 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D3">
         <v>328.48500000000001</v>
@@ -691,34 +709,34 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D5">
-        <v>540</v>
+        <v>531.08999999999992</v>
       </c>
       <c r="E5">
-        <v>131.52186130069785</v>
+        <v>6.0952604538280424</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>17.100000000000001</v>
+        <v>51.24</v>
       </c>
       <c r="H5">
-        <v>4.5254833995939059</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>-363.45</v>
+        <v>-396.29999999999995</v>
       </c>
       <c r="K5">
-        <v>15.700212312789498</v>
+        <v>18.966988866624746</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -726,34 +744,34 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6">
-        <v>531.08999999999992</v>
-      </c>
-      <c r="E6">
-        <v>6.0952604538280424</v>
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>2</v>
-      </c>
-      <c r="G6">
-        <v>51.24</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>2</v>
       </c>
       <c r="I6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>-396.29999999999995</v>
+        <v>-316.17500000000001</v>
       </c>
       <c r="K6">
-        <v>18.966988866624746</v>
+        <v>12.790198069876276</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -761,19 +779,19 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="D7">
+        <v>264.14999999999998</v>
       </c>
       <c r="E7" t="s">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="s">
         <v>2</v>
@@ -784,40 +802,40 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
-        <v>-316.17500000000001</v>
-      </c>
-      <c r="K7">
-        <v>12.790198069876276</v>
+      <c r="J7" t="s">
+        <v>2</v>
+      </c>
+      <c r="K7" t="s">
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D8">
-        <v>264.14999999999998</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2</v>
+        <v>373.875</v>
+      </c>
+      <c r="E8">
+        <v>4.6315494167718541</v>
       </c>
       <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G8">
+        <v>13.749600000000001</v>
+      </c>
+      <c r="H8">
+        <v>3.0399934736772081</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8" t="s">
         <v>2</v>
@@ -831,69 +849,69 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9">
-        <v>373.875</v>
-      </c>
-      <c r="E9">
-        <v>4.6315494167718541</v>
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>2</v>
-      </c>
-      <c r="G9">
-        <v>13.749600000000001</v>
-      </c>
-      <c r="H9">
-        <v>3.0399934736772081</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>2</v>
       </c>
       <c r="I9">
-        <v>2</v>
-      </c>
-      <c r="J9" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>-256.83333333333331</v>
+      </c>
+      <c r="K9">
+        <v>9.6738479072876338</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>639.63</v>
+      </c>
+      <c r="E10">
+        <v>46.349679610543141</v>
       </c>
       <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>20.49</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>-256.83333333333331</v>
+        <v>-274.8</v>
       </c>
       <c r="K10">
-        <v>9.6738479072876338</v>
+        <v>2.4331050121192805</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -901,34 +919,34 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11">
-        <v>639.63</v>
-      </c>
-      <c r="E11">
-        <v>46.349679610543141</v>
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2</v>
       </c>
       <c r="F11">
-        <v>3</v>
-      </c>
-      <c r="G11">
-        <v>20.49</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>-274.8</v>
+        <v>-199.13333333333333</v>
       </c>
       <c r="K11">
-        <v>2.4331050121192805</v>
+        <v>7.9122268251948746</v>
       </c>
       <c r="L11">
         <v>3</v>
@@ -936,63 +954,63 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>2</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="D12">
+        <v>376.02499999999998</v>
+      </c>
+      <c r="E12">
+        <v>0.17677669529663689</v>
       </c>
       <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2</v>
-      </c>
-      <c r="H12" t="s">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G12">
+        <v>40.760800000000003</v>
+      </c>
+      <c r="H12">
+        <v>0.93451232201614376</v>
       </c>
       <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>-199.13333333333333</v>
-      </c>
-      <c r="K12">
-        <v>7.9122268251948746</v>
+        <v>2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>2</v>
+      </c>
+      <c r="K12" t="s">
+        <v>2</v>
       </c>
       <c r="L12">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13">
-        <v>376.02499999999998</v>
-      </c>
-      <c r="E13">
-        <v>0.17677669529663689</v>
+        <v>295.14999999999998</v>
+      </c>
+      <c r="E13" t="s">
+        <v>2</v>
       </c>
       <c r="F13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>40.760800000000003</v>
-      </c>
-      <c r="H13">
-        <v>0.93451232201614376</v>
+        <v>1.29704</v>
+      </c>
+      <c r="H13" t="s">
+        <v>2</v>
       </c>
       <c r="I13">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J13" t="s">
         <v>2</v>
@@ -1006,13 +1024,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14">
-        <v>295.14999999999998</v>
+        <v>412.15</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
@@ -1021,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>1.29704</v>
+        <v>39.329600000000006</v>
       </c>
       <c r="H14" t="s">
         <v>2</v>
@@ -1041,13 +1059,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D15">
-        <v>412.15</v>
+        <v>583</v>
       </c>
       <c r="E15" t="s">
         <v>2</v>
@@ -1056,7 +1074,7 @@
         <v>1</v>
       </c>
       <c r="G15">
-        <v>39.329600000000006</v>
+        <v>7.3</v>
       </c>
       <c r="H15" t="s">
         <v>2</v>
@@ -1064,113 +1082,113 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="J15" t="s">
-        <v>2</v>
+      <c r="J15">
+        <v>-442</v>
       </c>
       <c r="K15" t="s">
         <v>2</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D16">
-        <v>583</v>
-      </c>
-      <c r="E16" t="s">
-        <v>2</v>
+        <v>473.87333333333328</v>
+      </c>
+      <c r="E16">
+        <v>49.990995522527193</v>
       </c>
       <c r="F16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16">
-        <v>7.3</v>
-      </c>
-      <c r="H16" t="s">
-        <v>2</v>
+        <v>66.58</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J16">
-        <v>-442</v>
-      </c>
-      <c r="K16" t="s">
-        <v>2</v>
+        <v>-487.5</v>
+      </c>
+      <c r="K16">
+        <v>17.677669529663689</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
-      </c>
-      <c r="D17">
-        <v>473.87333333333328</v>
-      </c>
-      <c r="E17">
-        <v>49.990995522527193</v>
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E17" t="s">
+        <v>2</v>
       </c>
       <c r="F17">
-        <v>3</v>
-      </c>
-      <c r="G17">
-        <v>66.58</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G17" t="s">
+        <v>2</v>
+      </c>
+      <c r="H17" t="s">
+        <v>2</v>
       </c>
       <c r="I17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-487.5</v>
-      </c>
-      <c r="K17">
-        <v>17.677669529663689</v>
+        <v>-395</v>
+      </c>
+      <c r="K17" t="s">
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2</v>
+        <v>48</v>
+      </c>
+      <c r="D18">
+        <v>673.15</v>
       </c>
       <c r="E18" t="s">
         <v>2</v>
       </c>
       <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>16</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>-395</v>
+        <v>-191.84</v>
       </c>
       <c r="K18" t="s">
         <v>2</v>
@@ -1181,13 +1199,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D19">
-        <v>673.15</v>
+        <v>878.15</v>
       </c>
       <c r="E19" t="s">
         <v>2</v>
@@ -1196,7 +1214,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>16</v>
+        <v>19.2</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
@@ -1205,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>-191.84</v>
+        <v>-226.9</v>
       </c>
       <c r="K19" t="s">
         <v>2</v>
@@ -1222,7 +1240,7 @@
         <v>44</v>
       </c>
       <c r="D20">
-        <v>878.15</v>
+        <v>559.15</v>
       </c>
       <c r="E20" t="s">
         <v>2</v>
@@ -1231,7 +1249,7 @@
         <v>1</v>
       </c>
       <c r="G20">
-        <v>19.2</v>
+        <v>7.14</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
@@ -1240,7 +1258,7 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>-226.9</v>
+        <v>-190.46</v>
       </c>
       <c r="K20" t="s">
         <v>2</v>
@@ -1251,22 +1269,22 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D21">
-        <v>559.15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2</v>
+        <v>881.15</v>
+      </c>
+      <c r="E21">
+        <v>6.2449979983983983</v>
       </c>
       <c r="F21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21">
-        <v>7.14</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
@@ -1275,7 +1293,7 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>-190.46</v>
+        <v>-408.6</v>
       </c>
       <c r="K21" t="s">
         <v>2</v>
@@ -1286,22 +1304,22 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>881.15</v>
+        <v>1045.1500000000001</v>
       </c>
       <c r="E22">
-        <v>6.2449979983983983</v>
+        <v>1.4142135623730951</v>
       </c>
       <c r="F22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22">
-        <v>19.899999999999999</v>
+        <v>26.317360000000001</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
@@ -1310,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>-408.6</v>
+        <v>-436.68</v>
       </c>
       <c r="K22" t="s">
         <v>2</v>
@@ -1321,22 +1339,22 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D23">
-        <v>1045.1500000000001</v>
+        <v>1074.075</v>
       </c>
       <c r="E23">
-        <v>1.4142135623730951</v>
+        <v>8.6602540378496379E-2</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G23">
-        <v>26.317360000000001</v>
+        <v>30.388680025600006</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
@@ -1345,33 +1363,33 @@
         <v>1</v>
       </c>
       <c r="J23">
-        <v>-436.68</v>
-      </c>
-      <c r="K23" t="s">
-        <v>2</v>
+        <v>-411.01</v>
+      </c>
+      <c r="K23">
+        <v>0.15556349186105975</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D24">
-        <v>1074.075</v>
-      </c>
-      <c r="E24">
-        <v>8.6602540378496379E-2</v>
+        <v>243.24999999999997</v>
+      </c>
+      <c r="E24" t="s">
+        <v>2</v>
       </c>
       <c r="F24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G24">
-        <v>30.388680025600006</v>
+        <v>10.9</v>
       </c>
       <c r="H24" t="s">
         <v>2</v>
@@ -1379,14 +1397,119 @@
       <c r="I24">
         <v>1</v>
       </c>
-      <c r="J24">
-        <v>-411.01</v>
-      </c>
-      <c r="K24">
-        <v>0.15556349186105975</v>
+      <c r="J24" t="s">
+        <v>2</v>
+      </c>
+      <c r="K24" t="s">
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>2</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25">
+        <v>281.64999999999998</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>15.4</v>
+      </c>
+      <c r="H25" t="s">
+        <v>2</v>
+      </c>
+      <c r="I25">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>2</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C26" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26">
+        <v>307.84999999999997</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>23.6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>2</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>2</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27">
+        <v>323.04999999999995</v>
+      </c>
+      <c r="E27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27">
+        <v>30.7</v>
+      </c>
+      <c r="H27" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>2</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
+++ b/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\MTGPR_Tm_Hfus_Hf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E4B8203-B464-4025-BF9F-E8A8C5D32FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31EC1A6-D73F-4331-8335-FC8251437A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{535DD4A0-2912-47A9-820B-218FC7178EC0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
   <si>
     <t>tetrabutylammonium bromide</t>
   </si>
@@ -210,6 +210,30 @@
   </si>
   <si>
     <t>CCCCCCCCN.[B]</t>
+  </si>
+  <si>
+    <t>trimethylamine borane</t>
+  </si>
+  <si>
+    <t>[B].CN(C)C</t>
+  </si>
+  <si>
+    <t>dimethylamine borane</t>
+  </si>
+  <si>
+    <t>[B].CNC</t>
+  </si>
+  <si>
+    <t>dimethylamine</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
+    <t>trimethylamine</t>
+  </si>
+  <si>
+    <t>CN(C)C</t>
   </si>
 </sst>
 </file>
@@ -251,7 +275,30 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -581,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4AABDE-AFF5-4072-A990-39ABD46EABEB}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -1512,6 +1559,146 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28">
+        <v>366.65</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>2</v>
+      </c>
+      <c r="H28" t="s">
+        <v>2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>2</v>
+      </c>
+      <c r="K28" t="s">
+        <v>2</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29">
+        <v>310.14999999999998</v>
+      </c>
+      <c r="E29" t="s">
+        <v>2</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>2</v>
+      </c>
+      <c r="H29" t="s">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>2</v>
+      </c>
+      <c r="K29" t="s">
+        <v>2</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30">
+        <v>179.32</v>
+      </c>
+      <c r="E30">
+        <v>1.3349157276772183</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>5.9405000000000001</v>
+      </c>
+      <c r="H30">
+        <v>7.0710678118615568E-4</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>-21.4</v>
+      </c>
+      <c r="K30">
+        <v>3.3941125496954587</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31">
+        <v>153.26</v>
+      </c>
+      <c r="E31">
+        <v>3.6390932936653244</v>
+      </c>
+      <c r="F31">
+        <v>5</v>
+      </c>
+      <c r="G31">
+        <v>6.5419999999999998</v>
+      </c>
+      <c r="H31">
+        <v>2.8284271247458787E-3</v>
+      </c>
+      <c r="I31">
+        <v>2</v>
+      </c>
+      <c r="J31">
+        <v>-27.2</v>
+      </c>
+      <c r="K31">
+        <v>4.9497474683058327</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
+++ b/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\MTGPR_Tm_Hfus_Hf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31EC1A6-D73F-4331-8335-FC8251437A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0803DD36-E3AD-4526-B28D-58F09F404269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{535DD4A0-2912-47A9-820B-218FC7178EC0}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="59">
   <si>
     <t>tetrabutylammonium bromide</t>
   </si>
@@ -89,12 +89,6 @@
     <t>tetraethylammonium iodide</t>
   </si>
   <si>
-    <t>tetraheptylammonium chloride</t>
-  </si>
-  <si>
-    <t>tetrahexylammonium bromide</t>
-  </si>
-  <si>
     <t>tetramethylammonium bromide</t>
   </si>
   <si>
@@ -119,12 +113,6 @@
     <t>CC[N+](CC)(CC)CC.[I-]</t>
   </si>
   <si>
-    <t>CCCCCCC[N+](CCCCCCC)(CCCCCCC)CCCCCCC.[Cl-]</t>
-  </si>
-  <si>
-    <t>CCCCCC[N+](CCCCCC)(CCCCCC)CCCCCC.[Br-]</t>
-  </si>
-  <si>
     <t>C[N+](C)(C)C.[Br-]</t>
   </si>
   <si>
@@ -224,29 +212,29 @@
     <t>[B].CNC</t>
   </si>
   <si>
-    <t>dimethylamine</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>trimethylamine</t>
-  </si>
-  <si>
-    <t>CN(C)C</t>
+    <t>tetraethylammonium bromide</t>
+  </si>
+  <si>
+    <t>CC[N+](CC)(CC)CC.[Br-]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -269,36 +257,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -628,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4AABDE-AFF5-4072-A990-39ABD46EABEB}">
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -755,35 +723,35 @@
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
+      <c r="A5" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D5">
-        <v>531.08999999999992</v>
+        <v>540</v>
       </c>
       <c r="E5">
-        <v>6.0952604538280424</v>
+        <v>131.52186130069785</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <v>51.24</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>4.5254833995939059</v>
       </c>
       <c r="I5">
         <v>2</v>
       </c>
       <c r="J5">
-        <v>-396.29999999999995</v>
+        <v>-363.45</v>
       </c>
       <c r="K5">
-        <v>18.966988866624746</v>
+        <v>15.700212312789498</v>
       </c>
       <c r="L5">
         <v>4</v>
@@ -791,34 +759,34 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" t="s">
-        <v>2</v>
+        <v>42</v>
+      </c>
+      <c r="D6">
+        <v>531.08999999999992</v>
+      </c>
+      <c r="E6">
+        <v>6.0952604538280424</v>
       </c>
       <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H6" t="s">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>51.24</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>-316.17500000000001</v>
+        <v>-396.29999999999995</v>
       </c>
       <c r="K6">
-        <v>12.790198069876276</v>
+        <v>18.966988866624746</v>
       </c>
       <c r="L6">
         <v>4</v>
@@ -826,19 +794,19 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7">
-        <v>264.14999999999998</v>
+        <v>23</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
       </c>
       <c r="E7" t="s">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
         <v>2</v>
@@ -849,81 +817,81 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>2</v>
+      <c r="J7">
+        <v>-316.17500000000001</v>
+      </c>
+      <c r="K7">
+        <v>12.790198069876276</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8">
-        <v>373.875</v>
-      </c>
-      <c r="E8">
-        <v>4.6315494167718541</v>
+        <v>24</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>2</v>
-      </c>
-      <c r="G8">
-        <v>13.749600000000001</v>
-      </c>
-      <c r="H8">
-        <v>3.0399934736772081</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
       </c>
       <c r="I8">
-        <v>2</v>
-      </c>
-      <c r="J8" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-256.83333333333331</v>
+      </c>
+      <c r="K8">
+        <v>9.6738479072876338</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2</v>
+        <v>10</v>
+      </c>
+      <c r="D9">
+        <v>639.63</v>
+      </c>
+      <c r="E9">
+        <v>46.349679610543141</v>
       </c>
       <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" t="s">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>20.49</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
-        <v>-256.83333333333331</v>
+        <v>-274.8</v>
       </c>
       <c r="K9">
-        <v>9.6738479072876338</v>
+        <v>2.4331050121192805</v>
       </c>
       <c r="L9">
         <v>3</v>
@@ -931,34 +899,34 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10">
-        <v>639.63</v>
-      </c>
-      <c r="E10">
-        <v>46.349679610543141</v>
+        <v>25</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>2</v>
       </c>
       <c r="F10">
-        <v>3</v>
-      </c>
-      <c r="G10">
-        <v>20.49</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G10" t="s">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>2</v>
       </c>
       <c r="I10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>-274.8</v>
+        <v>-199.13333333333333</v>
       </c>
       <c r="K10">
-        <v>2.4331050121192805</v>
+        <v>7.9122268251948746</v>
       </c>
       <c r="L10">
         <v>3</v>
@@ -966,63 +934,63 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2</v>
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>376.02499999999998</v>
+      </c>
+      <c r="E11">
+        <v>0.17677669529663689</v>
       </c>
       <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>2</v>
-      </c>
-      <c r="H11" t="s">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G11">
+        <v>40.760800000000003</v>
+      </c>
+      <c r="H11">
+        <v>0.93451232201614376</v>
       </c>
       <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>-199.13333333333333</v>
-      </c>
-      <c r="K11">
-        <v>7.9122268251948746</v>
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>2</v>
+      </c>
+      <c r="K11" t="s">
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D12">
-        <v>376.02499999999998</v>
-      </c>
-      <c r="E12">
-        <v>0.17677669529663689</v>
+        <v>295.14999999999998</v>
+      </c>
+      <c r="E12" t="s">
+        <v>2</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>40.760800000000003</v>
-      </c>
-      <c r="H12">
-        <v>0.93451232201614376</v>
+        <v>1.29704</v>
+      </c>
+      <c r="H12" t="s">
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J12" t="s">
         <v>2</v>
@@ -1036,13 +1004,13 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D13">
-        <v>295.14999999999998</v>
+        <v>412.15</v>
       </c>
       <c r="E13" t="s">
         <v>2</v>
@@ -1051,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="G13">
-        <v>1.29704</v>
+        <v>39.329600000000006</v>
       </c>
       <c r="H13" t="s">
         <v>2</v>
@@ -1071,13 +1039,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14">
-        <v>412.15</v>
+        <v>583</v>
       </c>
       <c r="E14" t="s">
         <v>2</v>
@@ -1086,7 +1054,7 @@
         <v>1</v>
       </c>
       <c r="G14">
-        <v>39.329600000000006</v>
+        <v>7.3</v>
       </c>
       <c r="H14" t="s">
         <v>2</v>
@@ -1094,113 +1062,113 @@
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="J14" t="s">
-        <v>2</v>
+      <c r="J14">
+        <v>-442</v>
       </c>
       <c r="K14" t="s">
         <v>2</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D15">
-        <v>583</v>
-      </c>
-      <c r="E15" t="s">
-        <v>2</v>
+        <v>473.87333333333328</v>
+      </c>
+      <c r="E15">
+        <v>49.990995522527193</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G15">
-        <v>7.3</v>
-      </c>
-      <c r="H15" t="s">
-        <v>2</v>
+        <v>66.58</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15">
-        <v>-442</v>
-      </c>
-      <c r="K15" t="s">
-        <v>2</v>
+        <v>-487.5</v>
+      </c>
+      <c r="K15">
+        <v>17.677669529663689</v>
       </c>
       <c r="L15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16">
-        <v>473.87333333333328</v>
-      </c>
-      <c r="E16">
-        <v>49.990995522527193</v>
+        <v>30</v>
+      </c>
+      <c r="D16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E16" t="s">
+        <v>2</v>
       </c>
       <c r="F16">
-        <v>3</v>
-      </c>
-      <c r="G16">
-        <v>66.58</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="G16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H16" t="s">
+        <v>2</v>
       </c>
       <c r="I16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J16">
-        <v>-487.5</v>
-      </c>
-      <c r="K16">
-        <v>17.677669529663689</v>
+        <v>-395</v>
+      </c>
+      <c r="K16" t="s">
+        <v>2</v>
       </c>
       <c r="L16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" t="s">
-        <v>2</v>
+        <v>44</v>
+      </c>
+      <c r="D17">
+        <v>673.15</v>
       </c>
       <c r="E17" t="s">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>0</v>
-      </c>
-      <c r="G17" t="s">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>16</v>
       </c>
       <c r="H17" t="s">
         <v>2</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>-395</v>
+        <v>-191.84</v>
       </c>
       <c r="K17" t="s">
         <v>2</v>
@@ -1211,13 +1179,13 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="D18">
-        <v>673.15</v>
+        <v>878.15</v>
       </c>
       <c r="E18" t="s">
         <v>2</v>
@@ -1226,7 +1194,7 @@
         <v>1</v>
       </c>
       <c r="G18">
-        <v>16</v>
+        <v>19.2</v>
       </c>
       <c r="H18" t="s">
         <v>2</v>
@@ -1235,7 +1203,7 @@
         <v>1</v>
       </c>
       <c r="J18">
-        <v>-191.84</v>
+        <v>-226.9</v>
       </c>
       <c r="K18" t="s">
         <v>2</v>
@@ -1246,13 +1214,13 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D19">
-        <v>878.15</v>
+        <v>559.15</v>
       </c>
       <c r="E19" t="s">
         <v>2</v>
@@ -1261,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="G19">
-        <v>19.2</v>
+        <v>7.14</v>
       </c>
       <c r="H19" t="s">
         <v>2</v>
@@ -1270,7 +1238,7 @@
         <v>1</v>
       </c>
       <c r="J19">
-        <v>-226.9</v>
+        <v>-190.46</v>
       </c>
       <c r="K19" t="s">
         <v>2</v>
@@ -1281,22 +1249,22 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D20">
-        <v>559.15</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2</v>
+        <v>881.15</v>
+      </c>
+      <c r="E20">
+        <v>6.2449979983983983</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>7.14</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H20" t="s">
         <v>2</v>
@@ -1305,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="J20">
-        <v>-190.46</v>
+        <v>-408.6</v>
       </c>
       <c r="K20" t="s">
         <v>2</v>
@@ -1322,16 +1290,16 @@
         <v>36</v>
       </c>
       <c r="D21">
-        <v>881.15</v>
+        <v>1045.1500000000001</v>
       </c>
       <c r="E21">
-        <v>6.2449979983983983</v>
+        <v>1.4142135623730951</v>
       </c>
       <c r="F21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21">
-        <v>19.899999999999999</v>
+        <v>26.317360000000001</v>
       </c>
       <c r="H21" t="s">
         <v>2</v>
@@ -1340,7 +1308,7 @@
         <v>1</v>
       </c>
       <c r="J21">
-        <v>-408.6</v>
+        <v>-436.68</v>
       </c>
       <c r="K21" t="s">
         <v>2</v>
@@ -1351,22 +1319,22 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D22">
-        <v>1045.1500000000001</v>
+        <v>1074.075</v>
       </c>
       <c r="E22">
-        <v>1.4142135623730951</v>
+        <v>8.6602540378496379E-2</v>
       </c>
       <c r="F22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22">
-        <v>26.317360000000001</v>
+        <v>30.388680025600006</v>
       </c>
       <c r="H22" t="s">
         <v>2</v>
@@ -1375,33 +1343,33 @@
         <v>1</v>
       </c>
       <c r="J22">
-        <v>-436.68</v>
-      </c>
-      <c r="K22" t="s">
-        <v>2</v>
+        <v>-411.01</v>
+      </c>
+      <c r="K22">
+        <v>0.15556349186105975</v>
       </c>
       <c r="L22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D23">
-        <v>1074.075</v>
-      </c>
-      <c r="E23">
-        <v>8.6602540378496379E-2</v>
+        <v>243.24999999999997</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2</v>
       </c>
       <c r="F23">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G23">
-        <v>30.388680025600006</v>
+        <v>10.9</v>
       </c>
       <c r="H23" t="s">
         <v>2</v>
@@ -1409,25 +1377,25 @@
       <c r="I23">
         <v>1</v>
       </c>
-      <c r="J23">
-        <v>-411.01</v>
-      </c>
-      <c r="K23">
-        <v>0.15556349186105975</v>
+      <c r="J23" t="s">
+        <v>2</v>
+      </c>
+      <c r="K23" t="s">
+        <v>2</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D24">
-        <v>243.24999999999997</v>
+        <v>281.64999999999998</v>
       </c>
       <c r="E24" t="s">
         <v>2</v>
@@ -1436,7 +1404,7 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>10.9</v>
+        <v>15.4</v>
       </c>
       <c r="H24" t="s">
         <v>2</v>
@@ -1462,7 +1430,7 @@
         <v>52</v>
       </c>
       <c r="D25">
-        <v>281.64999999999998</v>
+        <v>307.84999999999997</v>
       </c>
       <c r="E25" t="s">
         <v>2</v>
@@ -1471,7 +1439,7 @@
         <v>1</v>
       </c>
       <c r="G25">
-        <v>15.4</v>
+        <v>23.6</v>
       </c>
       <c r="H25" t="s">
         <v>2</v>
@@ -1491,13 +1459,13 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C26" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D26">
-        <v>307.84999999999997</v>
+        <v>323.04999999999995</v>
       </c>
       <c r="E26" t="s">
         <v>2</v>
@@ -1506,7 +1474,7 @@
         <v>1</v>
       </c>
       <c r="G26">
-        <v>23.6</v>
+        <v>30.7</v>
       </c>
       <c r="H26" t="s">
         <v>2</v>
@@ -1532,7 +1500,7 @@
         <v>54</v>
       </c>
       <c r="D27">
-        <v>323.04999999999995</v>
+        <v>366.65</v>
       </c>
       <c r="E27" t="s">
         <v>2</v>
@@ -1540,14 +1508,14 @@
       <c r="F27">
         <v>1</v>
       </c>
-      <c r="G27">
-        <v>30.7</v>
+      <c r="G27" t="s">
+        <v>2</v>
       </c>
       <c r="H27" t="s">
         <v>2</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="s">
         <v>2</v>
@@ -1561,13 +1529,13 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D28">
-        <v>366.65</v>
+        <v>310.14999999999998</v>
       </c>
       <c r="E28" t="s">
         <v>2</v>
@@ -1592,111 +1560,6 @@
       </c>
       <c r="L28">
         <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>59</v>
-      </c>
-      <c r="C29" t="s">
-        <v>60</v>
-      </c>
-      <c r="D29">
-        <v>310.14999999999998</v>
-      </c>
-      <c r="E29" t="s">
-        <v>2</v>
-      </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="s">
-        <v>2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>2</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29" t="s">
-        <v>2</v>
-      </c>
-      <c r="K29" t="s">
-        <v>2</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" t="s">
-        <v>62</v>
-      </c>
-      <c r="D30">
-        <v>179.32</v>
-      </c>
-      <c r="E30">
-        <v>1.3349157276772183</v>
-      </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30">
-        <v>5.9405000000000001</v>
-      </c>
-      <c r="H30">
-        <v>7.0710678118615568E-4</v>
-      </c>
-      <c r="I30">
-        <v>2</v>
-      </c>
-      <c r="J30">
-        <v>-21.4</v>
-      </c>
-      <c r="K30">
-        <v>3.3941125496954587</v>
-      </c>
-      <c r="L30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31">
-        <v>153.26</v>
-      </c>
-      <c r="E31">
-        <v>3.6390932936653244</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31">
-        <v>6.5419999999999998</v>
-      </c>
-      <c r="H31">
-        <v>2.8284271247458787E-3</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31">
-        <v>-27.2</v>
-      </c>
-      <c r="K31">
-        <v>4.9497474683058327</v>
-      </c>
-      <c r="L31">
-        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
+++ b/data/input/MTGPR_Tm_Hfus_Hf/train_TBABH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\aglotov\Eutectics\data\input\MTGPR_Tm_Hfus_Hf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0803DD36-E3AD-4526-B28D-58F09F404269}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A4688-11AF-49D0-A66A-79292FEC5418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{535DD4A0-2912-47A9-820B-218FC7178EC0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{535DD4A0-2912-47A9-820B-218FC7178EC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="63">
   <si>
     <t>tetrabutylammonium bromide</t>
   </si>
@@ -179,43 +179,55 @@
     <t>butylamine borane</t>
   </si>
   <si>
-    <t>CCCCN.[B]</t>
-  </si>
-  <si>
     <t>hexylamine borane</t>
   </si>
   <si>
-    <t>CCCCCCN.[B]</t>
-  </si>
-  <si>
     <t>decylamine borane</t>
   </si>
   <si>
-    <t>CCCCCCCCCCN.[B]</t>
-  </si>
-  <si>
     <t>octylamine borane</t>
   </si>
   <si>
-    <t>CCCCCCCCN.[B]</t>
-  </si>
-  <si>
     <t>trimethylamine borane</t>
   </si>
   <si>
-    <t>[B].CN(C)C</t>
-  </si>
-  <si>
     <t>dimethylamine borane</t>
   </si>
   <si>
-    <t>[B].CNC</t>
-  </si>
-  <si>
     <t>tetraethylammonium bromide</t>
   </si>
   <si>
     <t>CC[N+](CC)(CC)CC.[Br-]</t>
+  </si>
+  <si>
+    <t>CCCCN.B</t>
+  </si>
+  <si>
+    <t>CCCCCCN.B</t>
+  </si>
+  <si>
+    <t>CCCCCCCCN.B</t>
+  </si>
+  <si>
+    <t>CCCCCCCCCCN.B</t>
+  </si>
+  <si>
+    <t>B.CN(C)C</t>
+  </si>
+  <si>
+    <t>B.CNC</t>
+  </si>
+  <si>
+    <t>trimethylamine</t>
+  </si>
+  <si>
+    <t>CN(C)C</t>
+  </si>
+  <si>
+    <t>dimethylamine</t>
+  </si>
+  <si>
+    <t>CNC</t>
   </si>
 </sst>
 </file>
@@ -266,7 +278,30 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -596,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB4AABDE-AFF5-4072-A990-39ABD46EABEB}">
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="36.42578125" bestFit="1" customWidth="1"/>
@@ -724,10 +759,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>540</v>
@@ -1357,7 +1392,7 @@
         <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="D23">
         <v>243.24999999999997</v>
@@ -1389,10 +1424,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D24">
         <v>281.64999999999998</v>
@@ -1424,10 +1459,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C25" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>307.84999999999997</v>
@@ -1459,10 +1494,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="D26">
         <v>323.04999999999995</v>
@@ -1494,10 +1529,10 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>366.65</v>
@@ -1529,10 +1564,10 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D28">
         <v>310.14999999999998</v>
@@ -1560,6 +1595,76 @@
       </c>
       <c r="L28">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29">
+        <v>153.26</v>
+      </c>
+      <c r="E29">
+        <v>3.6390932936653244</v>
+      </c>
+      <c r="F29">
+        <v>5</v>
+      </c>
+      <c r="G29">
+        <v>6.5419999999999998</v>
+      </c>
+      <c r="H29">
+        <v>2.8284271247458787E-3</v>
+      </c>
+      <c r="I29">
+        <v>2</v>
+      </c>
+      <c r="J29">
+        <v>-27.2</v>
+      </c>
+      <c r="K29">
+        <v>4.9497474683058327</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" t="s">
+        <v>62</v>
+      </c>
+      <c r="D30">
+        <v>179.32</v>
+      </c>
+      <c r="E30">
+        <v>1.3349157276772183</v>
+      </c>
+      <c r="F30">
+        <v>5</v>
+      </c>
+      <c r="G30">
+        <v>5.9405000000000001</v>
+      </c>
+      <c r="H30">
+        <v>7.0710678118615568E-4</v>
+      </c>
+      <c r="I30">
+        <v>2</v>
+      </c>
+      <c r="J30">
+        <v>-21.4</v>
+      </c>
+      <c r="K30">
+        <v>3.3941125496954587</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
